--- a/02_加值成品/九下/九下3-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下3-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下3-2 大氣中的水　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三下學期 九下3-2 大氣中的水　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>空氣上升冷卻,水氣會？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>凝結成小水滴</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>凝結或凝華</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>雪、冰雹</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>有雲雨變化</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>成雲</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>雲是由什麼組成？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>小水滴或冰晶</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>鋒面</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>凝結或凝華</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>氣團</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>非水蒸氣</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>雲中水滴夠大會？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>冰晶</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>降下成雨</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>鋒面</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>降水</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>大範圍性質均勻的空氣是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>冷暖乾濕</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>氣團</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>小水滴或冰晶</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>氣團</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>冷暖氣團交會的界面是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>鋒面</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>凝結成小水滴</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>氣團</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>雪、冰雹</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>界面</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>鋒面附近天氣常？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>小水滴或冰晶</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>懸浮成雲不降</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>上升冷卻</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>有雲雨變化</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>多變</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>空氣要成雲需先？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>氣團</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>滯留鋒面</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>有雲雨變化</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>上升冷卻</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>上升</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>降水除了雨還有？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>雪、冰雹</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>凝結或凝華</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>鋒面</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>形式</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>雲是由小水滴或什麼組成？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>冰晶</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>凝結或凝華</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>上升冷卻</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>非水蒸氣</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>冷暖氣團交會的界面稱？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>小水滴或冰晶</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>凝結成小水滴</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>鋒面</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>界面</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下3-2 大氣中的水　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三下學期 九下3-2 大氣中的水　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>雲的形成第一步是空氣？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>有雲雨變化</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>小水滴或冰晶</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>冷暖乾濕</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>上升</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>抬升</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>鋒面為何常帶來降雨？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>冷暖氣團交會抬升成雲雨且風向溫度變化</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>冷暖氣團交會抬升成雲</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>冷暖氣團交會抬升成雲雨</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>受熱上升遇山抬升鋒面抬升</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>抬升</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>氣團有哪些性質差異？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>冰晶</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>小水滴或冰晶</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>氣團</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>冷暖乾濕</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>分類</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>高空溫度低使水氣？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>乾冷</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>小水滴或冰晶</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>氣團</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>凝結或凝華</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>成雲</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>梅雨與什麼有關？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>滯留鋒面</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>有雲雨變化</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>鋒面</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>凝結成小水滴</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>鋒面</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>雲是氣態的水嗎？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>不是</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>鋒面</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>冰晶</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>氣團</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>小水滴冰晶</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>水滴太小時會？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>凝結成小水滴</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>氣團</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>滯留鋒</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>懸浮成雲不降</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>懸浮</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>冷氣團通常較？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>乾冷</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>懸浮成雲不降</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>降下成雨</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>冰晶</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>性質</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>空氣要形成雲須先怎樣？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>上升冷卻</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>小水滴或冰晶</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>雪、冰雹</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>鋒面</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>抬升</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>梅雨主要與哪種鋒面有關？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>氣團</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>小水滴或冰晶</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>懸浮成雲不降</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>滯留鋒</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>鋒面</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下3-2 大氣中的水　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三下學期 九下3-2 大氣中的水　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>描述從水氣到降雨的完整過程？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>冷暖氣團交會抬升成雲雨且風向溫度變化</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>冷暖氣團交會抬升成雲</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>空氣上升冷卻水氣凝結成雲水滴變大降下</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>冷暖氣團交會抬升成雲雨</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>過程</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何鋒面附近天氣多變？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>滯留鋒面停留造成持續降雨</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>空氣上升冷卻水氣凝結成雲水滴變大降下</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>冷暖氣團交會抬升成雲雨且風向溫度變化</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>空氣上升冷卻凝結成雲水滴變大降下</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>鋒面</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>為何雲是水滴而非水蒸氣？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>冷暖氣團交會抬升成雲雨</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>水氣凝結成液態或固態小顆粒</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>空氣上升冷卻水氣凝結成雲水滴變大降下</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>冷暖氣團交會抬升成雲</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>狀態</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>梅雨季連日降雨與鋒面關係？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>滯留鋒面停留造成持續降雨</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>空氣上升冷卻凝結成雲水滴變大降下</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>水氣凝結成液態或固態小顆粒</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>受熱上升遇山抬升鋒面抬升</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>滯留鋒</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>空氣上升冷卻的常見原因？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>受熱上升遇山抬升鋒面抬升</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>水氣沿山坡抬升冷卻成雲</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>冷暖氣團交會抬升成雲雨且風向溫度變化</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>空氣上升冷卻凝結成雲水滴變大降下</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>抬升</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>氣團性質如何影響帶來的天氣？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>空氣上升冷卻水氣凝結成雲水滴變大降下</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>空氣上升冷卻凝結成雲水滴變大降下</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>冷乾帶晴冷暖濕帶悶熱多雨</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>冷暖氣團交會抬升成雲雨且風向溫度變化</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>影響</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>高山常見雲海形成原因？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>水氣沿山坡抬升冷卻成雲</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>冷乾帶晴冷暖濕帶悶熱多雨</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>空氣上升冷卻水氣凝結成雲水滴變大降下</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>冷暖氣團交會抬升成雲</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>地形</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>冰雹形成需要什麼條件？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>滯留鋒面停留造成持續降雨</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>空氣上升冷卻水氣凝結成雲水滴變大降下</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>強對流使冰晶反覆增大</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>冷暖氣團交會抬升成雲</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>對流</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>說明雨的形成過程？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>冷乾帶晴冷暖濕帶悶熱多雨</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>滯留鋒面停留造成持續降雨</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>空氣上升冷卻凝結成雲水滴變大降下</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>冷暖氣團交會抬升成雲雨且風向溫度變化</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>過程</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何鋒面附近常天氣多變？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>空氣上升冷卻水氣凝結成雲水滴變大降下</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>冷暖氣團交會抬升成雲</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>冷暖氣團交會抬升成雲雨</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>水氣凝結成液態或固態小顆粒</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>鋒面</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九下/九下3-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下3-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>成雲</t>
+          <t>成雲：空氣往上升時溫度會下降，裡面的水氣遇冷就會凝結成一顆顆很小的水滴</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>非水蒸氣</t>
+          <t>非水蒸氣：雲不是水蒸氣，而是由許多細小的水滴或冰晶聚集飄浮在空中組成的</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>降水</t>
+          <t>降水：雲裡的小水滴不斷合併變大，重到空氣托不住時就會落下形成雨</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>氣團</t>
+          <t>氣團：在廣大範圍內溫度、濕度等性質都差不多的一大團空氣，就稱為氣團</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>界面</t>
+          <t>界面：當冷氣團和暖氣團相遇碰在一起時，兩者之間的交界面就叫做鋒面</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>多變</t>
+          <t>多變：鋒面經過的地方，冷暖空氣互相推擠，天氣常常會出現雲量增加、下雨等變化</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>上升</t>
+          <t>上升：空氣必須先往上升、溫度隨之下降，裡面的水氣才會凝結形成雲</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>形式</t>
+          <t>形式：降水不只有雨這一種形式，在溫度更低時還可能形成雪或冰雹</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>非水蒸氣</t>
+          <t>非水蒸氣：雲其實是空氣中的水氣凝結成的小水滴或冰晶懸浮在空中,不是我們看不見的水蒸氣</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>界面</t>
+          <t>界面：性質不同的冷氣團和暖氣團相遇時,兩者之間的交界面就叫做鋒面</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>抬升</t>
+          <t>抬升：要形成雲，第一步通常是空氣受到某種原因被抬升到高空</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>冷暖氣團交會抬升成雲雨</t>
+          <t>冷暖氣團交會,暖空氣被迫抬升成雲致雨,且風向隨氣團更替而改變</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>抬升</t>
+          <t>抬升：冷暖氣團相遇時，較輕的暖空氣會被抬升到冷空氣上方，水氣因此凝結成雲並降雨</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>分類</t>
+          <t>分類：氣團可以依溫度分成冷、暖氣團，依含水氣多寡分成乾、濕氣團</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>成雲</t>
+          <t>成雲：高空溫度較低，水氣遇冷會凝結成小水滴，或直接凝華成小冰晶，形成雲</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>鋒面</t>
+          <t>鋒面：梅雨季節連續下雨，是因為冷暖氣團在同一地區交會，形成停留不動的滯留鋒面</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>小水滴冰晶</t>
+          <t>小水滴冰晶：雲並不是氣態的水蒸氣，而是由液態的小水滴或固態的小冰晶所組成</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>懸浮</t>
+          <t>懸浮：雲裡的水滴如果還很小、很輕，就會一直懸浮在空中形成雲，還不會降落成雨</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>性質</t>
+          <t>性質：來自高緯度或大陸內部的冷氣團，通常帶有比較乾燥又寒冷的性質</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>抬升</t>
+          <t>抬升：潮濕的空氣上升後因為壓力變小而膨脹冷卻,水氣才會凝結成小水滴形成雲</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>鋒面</t>
+          <t>滯留：梅雨季節時冷暖氣團勢力相當,鋒面在同一地區徘徊不太移動,形成滯留鋒帶來連日降雨</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>冷暖氣團交會抬升成雲雨</t>
+          <t>冷暖氣團交會,暖空氣被迫抬升成雲致雨,且風向隨氣團更替而改變</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>過程</t>
+          <t>過程：空氣先上升、溫度隨之下降，裡面的水氣凝結成小水滴聚集成雲，水滴不斷合併變大後，重到無法懸浮就降下成雨</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>鋒面</t>
+          <t>鋒面：鋒面附近冷暖氣團互相推擠交會，暖空氣被抬升凝結成雲雨，加上風向與氣溫也跟著改變，所以天氣容易多變</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>冷暖氣團交會抬升成雲雨</t>
+          <t>冷暖氣團交會,暖空氣被迫抬升成雲致雨,且風向隨氣團更替而改變</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>狀態</t>
+          <t>狀態：空氣中原本看不見的水氣，遇冷之後會凝結成看得見的液態小水滴或固態小冰晶，這才是我們看到的雲</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>滯留鋒</t>
+          <t>滯留鋒：梅雨季時冷暖氣團勢均力敵，在台灣附近長時間停留形成滯留鋒面，因此帶來連續多日的降雨</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>抬升</t>
+          <t>抬升：空氣受到地面加熱而上升、遇到山脈阻擋被迫爬升，或是被鋒面抬升，都是常見讓空氣上升冷卻的原因</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>影響</t>
+          <t>影響：性質乾冷的氣團籠罩時天氣通常晴朗寒冷，性質暖濕的氣團籠罩時則容易感覺悶熱且常有降雨</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>地形</t>
+          <t>地形：潮濕空氣沿著山坡往上爬升，途中溫度下降使水氣凝結成雲，聚集在山腰或山谷間就形成壯觀的雲海</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>對流</t>
+          <t>對流：雲層裡要有很強的上升氣流，讓小冰晶在雲中反覆被托起又下墜，不斷裹上水層凍結，才會逐漸長成冰雹</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>過程</t>
+          <t>過程：潮濕空氣上升後溫度下降,水氣凝結成小水滴聚集成雲,水滴不斷合併長大到空氣浮力撐不住時就落下成雨</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>為何鋒面附近常天氣多變？</t>
+          <t>鋒面通過時為何常伴隨降雨與風向轉變？</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1880,27 +1880,27 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>冷暖氣團交會抬升成雲</t>
+          <t>水氣凝結成液態或固態小顆粒</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>冷暖氣團交會抬升成雲雨</t>
+          <t>受熱上升遇山抬升鋒面抬升</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>水氣凝結成液態或固態小顆粒</t>
+          <t>冷暖氣團交會,暖空氣被迫抬升成雲致雨,且風向隨氣團更替而改變</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>鋒面</t>
+          <t>轉變：鋒面通過時,暖空氣被較重的冷空氣抬升冷卻凝結成雲雨;同時原本吹拂的氣團被另一氣團取代,風向也會跟著改變</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九下/九下3-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下3-2_三種難度測驗卷.xlsx
@@ -608,17 +608,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>鋒面</t>
+          <t>雪、冰雹</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>凝結或凝華</t>
+          <t>降下成雨</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>氣團</t>
+          <t>上升冷卻</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>凝結成小水滴</t>
+          <t>冷暖乾濕</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
+          <t>上升冷卻</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>氣團</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>雪、冰雹</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>氣團</t>
+          <t>凝結成小水滴</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>滯留鋒面</t>
+          <t>懸浮成雲不降</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>有雲雨變化</t>
+          <t>降下成雨</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>凝結或凝華</t>
+          <t>降下成雨</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>上升冷卻</t>
+          <t>冷暖乾濕</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>不是</t>
+          <t>鋒面</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
+          <t>有雲雨變化</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
           <t>上升</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>小水滴或冰晶</t>
-        </is>
-      </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>凝結成小水滴</t>
+          <t>乾冷</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>有雲雨變化</t>
+          <t>氣團</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>小水滴或冰晶</t>
+          <t>雪、冰雹</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>冷暖乾濕</t>
+          <t>降下成雨</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>冷暖氣團交會抬升成雲雨且風向溫度變化</t>
+          <t>冷暖氣團交會,暖空氣被迫抬升成雲致雨,且風向隨氣團更替而改變</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>冷暖氣團交會,暖空氣被迫抬升成雲致雨,且風向隨氣團更替而改變</t>
+          <t>空氣上升冷卻水氣凝結成雲水滴變大降下</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>受熱上升遇山抬升鋒面抬升</t>
+          <t>冷乾帶晴冷暖濕帶悶熱多雨</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1204,17 +1204,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>有雲雨變化</t>
+          <t>上升</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>鋒面</t>
+          <t>凝結成小水滴</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>凝結成小水滴</t>
+          <t>凝結或凝華</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>乾冷</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
           <t>小水滴或冰晶</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>雪、冰雹</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>鋒面</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>氣團</t>
+          <t>冷暖乾濕</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>小水滴或冰晶</t>
+          <t>懸浮成雲不降</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>懸浮成雲不降</t>
+          <t>降下成雨</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1555,22 +1555,22 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
+          <t>空氣上升冷卻水氣凝結成雲水滴變大降下</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>受熱上升遇山抬升鋒面抬升</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>冷暖氣團交會抬升成雲雨且風向溫度變化</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
           <t>滯留鋒面停留造成持續降雨</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>空氣上升冷卻水氣凝結成雲水滴變大降下</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>冷暖氣團交會抬升成雲雨且風向溫度變化</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>空氣上升冷卻凝結成雲水滴變大降下</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
